--- a/data/trans_orig/ProblemasDormirP33b-Edad-trans_orig.xlsx
+++ b/data/trans_orig/ProblemasDormirP33b-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con problemas para dormir a diario en 2023</t>
+          <t>Población con problemas para dormir a diario en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9948</t>
+          <t>9459</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41742</t>
+          <t>43218</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15603</t>
+          <t>14246</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46112</t>
+          <t>42436</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31170</t>
+          <t>30171</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72821</t>
+          <t>75214</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,55%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>358245</t>
+          <t>356769</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>390039</t>
+          <t>390528</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>267088</t>
+          <t>270764</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>297597</t>
+          <t>298954</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>640366</t>
+          <t>637973</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>682017</t>
+          <t>683016</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15884</t>
+          <t>17601</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42988</t>
+          <t>45453</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28065</t>
+          <t>26603</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64508</t>
+          <t>62484</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53285</t>
+          <t>54930</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>97037</t>
+          <t>98648</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>380559</t>
+          <t>378094</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>407663</t>
+          <t>405946</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>447585</t>
+          <t>449609</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>484028</t>
+          <t>485490</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>838603</t>
+          <t>836992</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>882355</t>
+          <t>880710</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,13%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43175</t>
+          <t>41738</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>72651</t>
+          <t>71826</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55094</t>
+          <t>55725</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88344</t>
+          <t>88697</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>107309</t>
+          <t>105849</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>154061</t>
+          <t>151845</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>463687</t>
+          <t>464512</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>493163</t>
+          <t>494600</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>503658</t>
+          <t>503305</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>536908</t>
+          <t>536277</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>974279</t>
+          <t>976495</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1021031</t>
+          <t>1022491</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,62%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32416</t>
+          <t>35440</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>115657</t>
+          <t>116778</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>115394</t>
+          <t>110327</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>158780</t>
+          <t>156040</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>127498</t>
+          <t>133236</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>265841</t>
+          <t>267926</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,74%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>772129</t>
+          <t>771008</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>855370</t>
+          <t>852346</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>554101</t>
+          <t>556841</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>597487</t>
+          <t>602554</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1334826</t>
+          <t>1332741</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1473169</t>
+          <t>1467431</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,68%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>74562</t>
+          <t>76202</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>106567</t>
+          <t>106849</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>136341</t>
+          <t>134294</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>166012</t>
+          <t>168524</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>218005</t>
+          <t>218795</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>263894</t>
+          <t>262843</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,7%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>454667</t>
+          <t>454385</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>486672</t>
+          <t>485032</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>381893</t>
+          <t>379381</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>411564</t>
+          <t>413611</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>845245</t>
+          <t>846296</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>891134</t>
+          <t>890344</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,27%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>55035</t>
+          <t>54100</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>77534</t>
+          <t>77409</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>45089</t>
+          <t>49368</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>173798</t>
+          <t>176316</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>95639</t>
+          <t>95689</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>233468</t>
+          <t>232702</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,83%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>290631</t>
+          <t>290756</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>313130</t>
+          <t>314065</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>434570</t>
+          <t>432052</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>563279</t>
+          <t>559000</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>743065</t>
+          <t>743831</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>880894</t>
+          <t>880844</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,2%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>64035</t>
+          <t>64114</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>87454</t>
+          <t>86938</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>137670</t>
+          <t>136430</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>166090</t>
+          <t>165249</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>207176</t>
+          <t>210399</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>243733</t>
+          <t>248029</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>35,0%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>195305</t>
+          <t>195821</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>218724</t>
+          <t>218645</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>259741</t>
+          <t>260582</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>288161</t>
+          <t>289401</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>464857</t>
+          <t>460561</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>501414</t>
+          <t>498191</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,31%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>333670</t>
+          <t>325701</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>466160</t>
+          <t>467253</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>564511</t>
+          <t>562143</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>760768</t>
+          <t>762810</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>966335</t>
+          <t>957431</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1205571</t>
+          <t>1205638</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2993657</t>
+          <t>2992564</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3126147</t>
+          <t>3134116</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2951512</t>
+          <t>2949470</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3147769</t>
+          <t>3150137</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5966526</t>
+          <t>5966459</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6205762</t>
+          <t>6214666</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,65%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/ProblemasDormirP33b-Edad-trans_orig.xlsx
+++ b/data/trans_orig/ProblemasDormirP33b-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>22376</t>
+          <t>24914</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9459</t>
+          <t>12123</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43218</t>
+          <t>43900</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>26262</t>
+          <t>32413</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14246</t>
+          <t>18400</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42436</t>
+          <t>50583</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>48638</t>
+          <t>57326</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30171</t>
+          <t>37668</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75214</t>
+          <t>81660</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>377611</t>
+          <t>382879</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>356769</t>
+          <t>363893</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>390528</t>
+          <t>395670</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>286938</t>
+          <t>330099</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>270764</t>
+          <t>311929</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>298954</t>
+          <t>344112</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>664549</t>
+          <t>712979</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>637973</t>
+          <t>688645</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>683016</t>
+          <t>732637</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,11%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28203</t>
+          <t>31522</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17601</t>
+          <t>19545</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45453</t>
+          <t>50842</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>46505</t>
+          <t>52070</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26603</t>
+          <t>39120</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62484</t>
+          <t>71101</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>74707</t>
+          <t>83593</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54930</t>
+          <t>64580</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>98648</t>
+          <t>107518</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>395344</t>
+          <t>445368</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>378094</t>
+          <t>426048</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>405946</t>
+          <t>457345</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>465588</t>
+          <t>449663</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>449609</t>
+          <t>430632</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>485490</t>
+          <t>462613</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>860933</t>
+          <t>895030</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>836992</t>
+          <t>871105</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>880710</t>
+          <t>914043</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,4%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>56237</t>
+          <t>60100</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41738</t>
+          <t>45886</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>71826</t>
+          <t>79428</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>73374</t>
+          <t>88424</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55725</t>
+          <t>74781</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88697</t>
+          <t>104460</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>129611</t>
+          <t>148524</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>105849</t>
+          <t>128800</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>151845</t>
+          <t>174486</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>480101</t>
+          <t>560737</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>464512</t>
+          <t>541409</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>494600</t>
+          <t>574951</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>518628</t>
+          <t>534769</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>503305</t>
+          <t>518733</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>536277</t>
+          <t>548412</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>998729</t>
+          <t>1095505</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>976495</t>
+          <t>1069543</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1022491</t>
+          <t>1115229</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>89,65%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>77921</t>
+          <t>86182</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35440</t>
+          <t>70813</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>116778</t>
+          <t>107913</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>137468</t>
+          <t>145261</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>110327</t>
+          <t>128840</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>156040</t>
+          <t>163038</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>215389</t>
+          <t>231444</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>133236</t>
+          <t>205969</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>267926</t>
+          <t>257512</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,91%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>809865</t>
+          <t>614435</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>771008</t>
+          <t>592704</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>852346</t>
+          <t>629804</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>575413</t>
+          <t>591625</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>556841</t>
+          <t>573848</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>602554</t>
+          <t>608046</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1385278</t>
+          <t>1206060</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1332741</t>
+          <t>1179992</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1467431</t>
+          <t>1231535</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>85,67%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>89600</t>
+          <t>95843</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>76202</t>
+          <t>79781</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>106849</t>
+          <t>114271</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>150677</t>
+          <t>168478</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>134294</t>
+          <t>149952</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>168524</t>
+          <t>184990</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>240277</t>
+          <t>264321</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>218795</t>
+          <t>239985</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>262843</t>
+          <t>289048</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>471634</t>
+          <t>513503</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>454385</t>
+          <t>495075</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>485032</t>
+          <t>529565</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>397228</t>
+          <t>440377</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>379381</t>
+          <t>423865</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>413611</t>
+          <t>458903</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>868862</t>
+          <t>953881</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>846296</t>
+          <t>929154</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>890344</t>
+          <t>978217</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,3%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>66078</t>
+          <t>74938</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54100</t>
+          <t>62520</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>77409</t>
+          <t>87947</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>111957</t>
+          <t>124084</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49368</t>
+          <t>110438</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>176316</t>
+          <t>137250</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>178035</t>
+          <t>199021</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>95689</t>
+          <t>181528</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>232702</t>
+          <t>219194</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>25,9%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>302087</t>
+          <t>332142</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>290756</t>
+          <t>319133</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>314065</t>
+          <t>344560</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>496411</t>
+          <t>315082</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>432052</t>
+          <t>301916</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>559000</t>
+          <t>328728</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>798498</t>
+          <t>647225</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>743831</t>
+          <t>627052</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>880844</t>
+          <t>664718</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>78,55%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>75299</t>
+          <t>84368</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>64114</t>
+          <t>72743</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>86938</t>
+          <t>99258</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>151052</t>
+          <t>167387</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>136430</t>
+          <t>152135</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>165249</t>
+          <t>183059</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>226351</t>
+          <t>251754</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>210399</t>
+          <t>231577</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>248029</t>
+          <t>271701</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,07%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>207460</t>
+          <t>225830</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>195821</t>
+          <t>210940</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>218645</t>
+          <t>237455</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>274779</t>
+          <t>297222</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>260582</t>
+          <t>281550</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>289401</t>
+          <t>312474</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>482239</t>
+          <t>523053</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>460561</t>
+          <t>503106</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>498191</t>
+          <t>543230</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,11%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>415715</t>
+          <t>457867</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>325701</t>
+          <t>417781</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>467253</t>
+          <t>501711</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>697294</t>
+          <t>778116</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>562143</t>
+          <t>738160</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>762810</t>
+          <t>822248</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1113009</t>
+          <t>1235984</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>957431</t>
+          <t>1172707</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1205638</t>
+          <t>1295263</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3044102</t>
+          <t>3074895</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2992564</t>
+          <t>3031051</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3134116</t>
+          <t>3114981</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3014986</t>
+          <t>2958838</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2949470</t>
+          <t>2914706</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3150137</t>
+          <t>2998794</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6059088</t>
+          <t>6033732</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5966459</t>
+          <t>5974453</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6214666</t>
+          <t>6097009</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>83,87%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
